--- a/school_surveys/029_student_financial_wellness_survey--school_surveys.xlsx
+++ b/school_surveys/029_student_financial_wellness_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'pell_grant'}</t>
+          <t>pell_grant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Pell Grant'}</t>
+          <t>Pell Grant</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'federal_work-study'}</t>
+          <t>federal_work-study</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Federal Work-Study'}</t>
+          <t>Federal Work-Study</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'federal_perkins_loan'}</t>
+          <t>federal_perkins_loan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Federal Perkins Loan'}</t>
+          <t>Federal Perkins Loan</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'institutional'}</t>
+          <t>institutional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Institutional'}</t>
+          <t>Institutional</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'financial_literacy'}</t>
+          <t>financial_literacy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Financial Literacy'}</t>
+          <t>Financial Literacy</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'financial_planning'}</t>
+          <t>financial_planning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Financial Planning'}</t>
+          <t>Financial Planning</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'financial_wellness_program'}</t>
+          <t>financial_wellness_program</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Financial Wellness Program'}</t>
+          <t>Financial Wellness Program</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'academic_advising'}</t>
+          <t>academic_advising</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Academic Advising'}</t>
+          <t>Academic Advising</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'career_counseling'}</t>
+          <t>career_counseling</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Career Counseling'}</t>
+          <t>Career Counseling</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'financial_aid_office'}</t>
+          <t>financial_aid_office</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Financial Aid Office'}</t>
+          <t>Financial Aid Office</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'student_life'}</t>
+          <t>student_life</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Student Life'}</t>
+          <t>Student Life</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
